--- a/skillsprogressiontable_18-8-25.xlsx
+++ b/skillsprogressiontable_18-8-25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gla-my.sharepoint.com/personal/helena_paterson_glasgow_ac_uk/Documents/Documents/assessmentai/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="248" documentId="13_ncr:1_{1F80AE8C-8A3C-FD4D-A675-5315F92D8B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A550009A-A8E3-42AF-A887-74EBB73AB074}"/>
+  <xr:revisionPtr revIDLastSave="251" documentId="13_ncr:1_{1F80AE8C-8A3C-FD4D-A675-5315F92D8B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25E6CBBF-42D1-4182-B2DB-84289DCAD62A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3FD2D535-207D-B548-9150-2445C489AFDF}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{3FD2D535-207D-B548-9150-2445C489AFDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="209">
   <si>
     <t>1st Year - Laboratory Practical</t>
   </si>
@@ -662,6 +662,33 @@
   </si>
   <si>
     <t>GenAI generated reference lists can take more time to check for accuracy than searches such as Web of Science and Google Scholar because hallucinations can take multiple forms: 1) completely invented reference; 2) invented digital object identifier even if the rest of the reference is correct; 3) some details of the citation correct but others invented (e.g. wrong journal); 4) improper formatting of citations or bibliography.  Directly copying whole sentences and paragraphs of an GenAI-assisted introduction is a form of academic misconduct, even if the tool used is cited.  Over-reliance on GenAI reduces development of  skills in information synthesis and critical analysis.</t>
+  </si>
+  <si>
+    <t>Students provided with a scenario of observations and asked to provide a hypothesis to explain the pattern, based on background information provided.</t>
+  </si>
+  <si>
+    <t>Could be used for inspiration about hypothesis but students should write in their own words.</t>
+  </si>
+  <si>
+    <t>Relying on GenAI for interpretation risks reducing development of critical analysis skills.  GenAI could provide misleading or inaccurate interpretations of the results.</t>
+  </si>
+  <si>
+    <t>Individuals asked to decide on most appropriate graphics to visualise results; in consultation with course organisers and examples, students asked to develop R code for data visualisation.</t>
+  </si>
+  <si>
+    <t>Could be consulted for inspiration on most appropriate visualisation,  for assistance with generating R code to produce plots and for trouble-shooting.</t>
+  </si>
+  <si>
+    <t>Inspiration for questions to ask supervisor or possible hypotheses to test on the topic of interest. Students should formulate their own objectives and hypotheses but could consult GenAI for improvement in clarity (but avoiding directly copying advice).</t>
+  </si>
+  <si>
+    <t>In consultation with supervisor, independent design of experiment on given topic.</t>
+  </si>
+  <si>
+    <t>Not helpful, except for advice on organising datasheets for particular analyses.</t>
+  </si>
+  <si>
+    <t>In consultation with supervisor and taking advantage of broader statistical support provided to students by the school, independent choice and application of appropriate statistical methods, including preparation of detailed, annotated R scripts (where appropriate).</t>
   </si>
 </sst>
 </file>
@@ -779,10 +806,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -790,18 +817,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -811,6 +826,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1174,47 +1201,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="109.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="O2" s="25" t="s">
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="O2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
       <c r="T2" s="4"/>
-      <c r="U2" s="23" t="s">
+      <c r="U2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1971,6 +1998,18 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="L12:L13"/>
     <mergeCell ref="U2:Y2"/>
     <mergeCell ref="U13:U14"/>
     <mergeCell ref="V13:V14"/>
@@ -1983,18 +2022,6 @@
     <mergeCell ref="Y13:Y14"/>
     <mergeCell ref="R13:R14"/>
     <mergeCell ref="X13:X14"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="L12:L13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2006,13 +2033,13 @@
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2065,10 +2092,10 @@
         <v>18</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>112</v>
@@ -2218,7 +2245,7 @@
         <v>101</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>102</v>
+        <v>202</v>
       </c>
       <c r="G11" s="17" t="s">
         <v>141</v>
@@ -2268,13 +2295,13 @@
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
     </row>
     <row r="2" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
@@ -2489,13 +2516,13 @@
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5" ht="78" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
@@ -2621,10 +2648,10 @@
         <v>56</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>57</v>
+        <v>204</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>100</v>
@@ -2710,13 +2737,13 @@
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
@@ -2760,7 +2787,7 @@
         <v>176</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>91</v>
+        <v>205</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>115</v>
@@ -2774,7 +2801,7 @@
         <v>28</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>29</v>
@@ -2811,7 +2838,7 @@
         <v>180</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>96</v>
@@ -2859,7 +2886,7 @@
         <v>66</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>138</v>
